--- a/data/templates/monthly_report_format_20260529.xlsx
+++ b/data/templates/monthly_report_format_20260529.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaito/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaito/個人開発アプリ/business-operations-tools/monthly-report-tool/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA71135-14E6-114D-BD78-2999D53C7DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F37E100-5976-7944-AA81-06EB8ADE7196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="3060" windowWidth="27500" windowHeight="16360" xr2:uid="{3886BC4A-148D-7140-9EB5-6B35F1965196}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>コード</t>
   </si>
   <si>
-    <t>名称</t>
-  </si>
-  <si>
     <t>売上サマリー</t>
   </si>
   <si>
@@ -123,6 +120,13 @@
   </si>
   <si>
     <t>所感</t>
+  </si>
+  <si>
+    <t>報告書タイプ</t>
+    <rPh sb="0" eb="3">
+      <t>ホウコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -618,9 +622,9 @@
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -658,7 +662,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="7"/>
@@ -674,7 +678,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -684,15 +688,15 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -714,15 +718,15 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="5"/>
     </row>
@@ -736,7 +740,7 @@
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -746,15 +750,15 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -776,15 +780,15 @@
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -798,7 +802,7 @@
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -808,15 +812,15 @@
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" s="5"/>
     </row>
@@ -830,7 +834,7 @@
     </row>
     <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -840,16 +844,16 @@
     </row>
     <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="7"/>
       <c r="F22" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1">
@@ -862,7 +866,7 @@
     </row>
     <row r="24" spans="1:6" ht="22" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
@@ -872,7 +876,7 @@
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
